--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3803"/>
+  <dimension ref="A1:E3804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103097,6 +103097,33 @@
         </is>
       </c>
     </row>
+    <row r="3804">
+      <c r="A3804" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3804" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3804" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3804" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3804" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3804"/>
+  <dimension ref="A1:E3805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103124,6 +103124,33 @@
         </is>
       </c>
     </row>
+    <row r="3805">
+      <c r="A3805" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3805" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3805" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3805" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3805" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3805"/>
+  <dimension ref="A1:E3806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103151,6 +103151,33 @@
         </is>
       </c>
     </row>
+    <row r="3806">
+      <c r="A3806" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3806" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3806" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3806" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3806" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3806"/>
+  <dimension ref="A1:E3807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103178,6 +103178,33 @@
         </is>
       </c>
     </row>
+    <row r="3807">
+      <c r="A3807" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3807" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3807" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3807" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3807" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3807"/>
+  <dimension ref="A1:E3808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103205,6 +103205,33 @@
         </is>
       </c>
     </row>
+    <row r="3808">
+      <c r="A3808" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3808" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3808" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3808" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3808" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3808"/>
+  <dimension ref="A1:E3809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103232,6 +103232,33 @@
         </is>
       </c>
     </row>
+    <row r="3809">
+      <c r="A3809" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3809" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3809" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3809" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3809" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3809"/>
+  <dimension ref="A1:E3810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103259,6 +103259,33 @@
         </is>
       </c>
     </row>
+    <row r="3810">
+      <c r="A3810" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3810" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3810" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D3810" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3810" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3810"/>
+  <dimension ref="A1:E3811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103286,6 +103286,33 @@
         </is>
       </c>
     </row>
+    <row r="3811">
+      <c r="A3811" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3811" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3811" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3811" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3811" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3811"/>
+  <dimension ref="A1:E3812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103313,6 +103313,33 @@
         </is>
       </c>
     </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3812" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3812" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3812" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3812" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3811"/>
+  <dimension ref="A1:E3812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -103310,6 +103322,33 @@
       <c r="E3811" t="inlineStr">
         <is>
           <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3812" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3812" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3812" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3812" t="inlineStr">
+        <is>
+          <t>87</t>
         </is>
       </c>
     </row>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3812"/>
+  <dimension ref="A1:E3813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103352,6 +103352,33 @@
         </is>
       </c>
     </row>
+    <row r="3813">
+      <c r="A3813" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3813" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3813" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3813" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3813" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3813"/>
+  <dimension ref="A1:E3814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103379,6 +103379,33 @@
         </is>
       </c>
     </row>
+    <row r="3814">
+      <c r="A3814" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3814" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3814" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3814" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3814" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3814"/>
+  <dimension ref="A1:E3815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103406,6 +103406,33 @@
         </is>
       </c>
     </row>
+    <row r="3815">
+      <c r="A3815" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3815" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3815" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3815" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3815" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3815"/>
+  <dimension ref="A1:E3816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103433,6 +103433,33 @@
         </is>
       </c>
     </row>
+    <row r="3816">
+      <c r="A3816" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3816" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3816" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D3816" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3816" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3816"/>
+  <dimension ref="A1:E3818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103460,6 +103460,60 @@
         </is>
       </c>
     </row>
+    <row r="3817">
+      <c r="A3817" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3817" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3817" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3817" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3817" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3818" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3818" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D3818" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3818" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3818"/>
+  <dimension ref="A1:E3819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103514,6 +103514,33 @@
         </is>
       </c>
     </row>
+    <row r="3819">
+      <c r="A3819" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3819" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3819" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3819" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3819" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3819"/>
+  <dimension ref="A1:E3820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103541,6 +103541,33 @@
         </is>
       </c>
     </row>
+    <row r="3820">
+      <c r="A3820" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3820" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3820" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3820" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3820" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3820"/>
+  <dimension ref="A1:E3821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103568,6 +103568,33 @@
         </is>
       </c>
     </row>
+    <row r="3821">
+      <c r="A3821" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3821" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3821" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3821" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3821" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3821"/>
+  <dimension ref="A1:E3822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103595,6 +103595,33 @@
         </is>
       </c>
     </row>
+    <row r="3822">
+      <c r="A3822" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3822" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3822" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3822" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E3822" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3822"/>
+  <dimension ref="A1:E3823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103622,6 +103622,33 @@
         </is>
       </c>
     </row>
+    <row r="3823">
+      <c r="A3823" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3823" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3823" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3823" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3823" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3823"/>
+  <dimension ref="A1:E3824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103649,6 +103649,33 @@
         </is>
       </c>
     </row>
+    <row r="3824">
+      <c r="A3824" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3824" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3824" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3824" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3824" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3824"/>
+  <dimension ref="A1:E3825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103676,6 +103676,33 @@
         </is>
       </c>
     </row>
+    <row r="3825">
+      <c r="A3825" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3825" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3825" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3825" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3825" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3825"/>
+  <dimension ref="A1:E3826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103703,6 +103703,33 @@
         </is>
       </c>
     </row>
+    <row r="3826">
+      <c r="A3826" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3826" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3826" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D3826" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3826" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3826"/>
+  <dimension ref="A1:E3827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103730,6 +103730,33 @@
         </is>
       </c>
     </row>
+    <row r="3827">
+      <c r="A3827" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3827" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3827" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3827" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3827" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3827"/>
+  <dimension ref="A1:E3828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103757,6 +103757,33 @@
         </is>
       </c>
     </row>
+    <row r="3828">
+      <c r="A3828" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3828" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3828" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3828" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3828" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3828"/>
+  <dimension ref="A1:E3829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103784,6 +103784,33 @@
         </is>
       </c>
     </row>
+    <row r="3829">
+      <c r="A3829" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3829" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3829" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3829" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3829" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3829"/>
+  <dimension ref="A1:E3830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103811,6 +103811,33 @@
         </is>
       </c>
     </row>
+    <row r="3830">
+      <c r="A3830" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3830" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3830" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3830" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3830" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3830"/>
+  <dimension ref="A1:E3831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103838,6 +103838,33 @@
         </is>
       </c>
     </row>
+    <row r="3831">
+      <c r="A3831" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3831" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3831" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3831" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3831" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3831"/>
+  <dimension ref="A1:E3832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103865,6 +103865,33 @@
         </is>
       </c>
     </row>
+    <row r="3832">
+      <c r="A3832" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3832" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3832" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D3832" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E3832" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3832"/>
+  <dimension ref="A1:E3833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103892,6 +103892,33 @@
         </is>
       </c>
     </row>
+    <row r="3833">
+      <c r="A3833" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3833" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3833" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D3833" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3833" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3833"/>
+  <dimension ref="A1:E3836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103919,6 +103919,87 @@
         </is>
       </c>
     </row>
+    <row r="3834">
+      <c r="A3834" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B3834" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3834" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D3834" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E3834" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B3835" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3835" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3835" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3835" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B3836" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3836" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3836" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3836" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3836"/>
+  <dimension ref="A1:E3837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104000,6 +104000,33 @@
         </is>
       </c>
     </row>
+    <row r="3837">
+      <c r="A3837" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B3837" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3837" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D3837" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3837" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3837"/>
+  <dimension ref="A1:E3838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104027,6 +104027,33 @@
         </is>
       </c>
     </row>
+    <row r="3838">
+      <c r="A3838" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B3838" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3838" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3838" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E3838" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3838"/>
+  <dimension ref="A1:E3839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104054,6 +104054,33 @@
         </is>
       </c>
     </row>
+    <row r="3839">
+      <c r="A3839" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B3839" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3839" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3839" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3839" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3839"/>
+  <dimension ref="A1:E3840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104081,6 +104081,33 @@
         </is>
       </c>
     </row>
+    <row r="3840">
+      <c r="A3840" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B3840" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3840" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3840" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3840" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3840"/>
+  <dimension ref="A1:E3841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104108,6 +104108,33 @@
         </is>
       </c>
     </row>
+    <row r="3841">
+      <c r="A3841" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B3841" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3841" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3841" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3841" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3841"/>
+  <dimension ref="A1:E3842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104135,6 +104135,33 @@
         </is>
       </c>
     </row>
+    <row r="3842">
+      <c r="A3842" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B3842" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3842" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3842" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3842" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3842"/>
+  <dimension ref="A1:E3843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104162,6 +104162,33 @@
         </is>
       </c>
     </row>
+    <row r="3843">
+      <c r="A3843" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B3843" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3843" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3843" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3843" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3843"/>
+  <dimension ref="A1:E3844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104189,6 +104189,33 @@
         </is>
       </c>
     </row>
+    <row r="3844">
+      <c r="A3844" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B3844" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3844" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3844" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3844" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3844"/>
+  <dimension ref="A1:E3845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104216,6 +104216,33 @@
         </is>
       </c>
     </row>
+    <row r="3845">
+      <c r="A3845" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B3845" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3845" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3845" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3845" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3845"/>
+  <dimension ref="A1:E3846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104243,6 +104243,33 @@
         </is>
       </c>
     </row>
+    <row r="3846">
+      <c r="A3846" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B3846" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3846" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3846" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3846" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3846"/>
+  <dimension ref="A1:E3847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104270,6 +104270,33 @@
         </is>
       </c>
     </row>
+    <row r="3847">
+      <c r="A3847" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B3847" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3847" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3847" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3847" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3847"/>
+  <dimension ref="A1:E3848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104297,6 +104297,33 @@
         </is>
       </c>
     </row>
+    <row r="3848">
+      <c r="A3848" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B3848" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3848" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3848" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3848" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3848"/>
+  <dimension ref="A1:E3849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104324,6 +104324,33 @@
         </is>
       </c>
     </row>
+    <row r="3849">
+      <c r="A3849" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B3849" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3849" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3849" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3849" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3849"/>
+  <dimension ref="A1:E3850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104351,6 +104351,33 @@
         </is>
       </c>
     </row>
+    <row r="3850">
+      <c r="A3850" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B3850" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3850" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D3850" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3850" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3850"/>
+  <dimension ref="A1:E3851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104378,6 +104378,33 @@
         </is>
       </c>
     </row>
+    <row r="3851">
+      <c r="A3851" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B3851" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3851" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3851" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3851" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3851"/>
+  <dimension ref="A1:E3852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104405,6 +104405,33 @@
         </is>
       </c>
     </row>
+    <row r="3852">
+      <c r="A3852" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B3852" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3852" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3852" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3852" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3852"/>
+  <dimension ref="A1:E3853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104432,6 +104432,33 @@
         </is>
       </c>
     </row>
+    <row r="3853">
+      <c r="A3853" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B3853" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3853" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3853" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3853" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3853"/>
+  <dimension ref="A1:E3854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104459,6 +104459,33 @@
         </is>
       </c>
     </row>
+    <row r="3854">
+      <c r="A3854" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B3854" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3854" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D3854" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3854" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3854"/>
+  <dimension ref="A1:E3855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104486,6 +104486,33 @@
         </is>
       </c>
     </row>
+    <row r="3855">
+      <c r="A3855" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B3855" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3855" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D3855" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3855" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3855"/>
+  <dimension ref="A1:E3856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104513,6 +104513,33 @@
         </is>
       </c>
     </row>
+    <row r="3856">
+      <c r="A3856" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B3856" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3856" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3856" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3856" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3856"/>
+  <dimension ref="A1:E3857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104540,6 +104540,33 @@
         </is>
       </c>
     </row>
+    <row r="3857">
+      <c r="A3857" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B3857" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3857" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D3857" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3857" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3857"/>
+  <dimension ref="A1:E3858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104567,6 +104567,33 @@
         </is>
       </c>
     </row>
+    <row r="3858">
+      <c r="A3858" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3858" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3858" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3858" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3858" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3858"/>
+  <dimension ref="A1:E3859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104594,6 +104594,33 @@
         </is>
       </c>
     </row>
+    <row r="3859">
+      <c r="A3859" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3859" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3859" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3859" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3859" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3859"/>
+  <dimension ref="A1:E3860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104621,6 +104621,33 @@
         </is>
       </c>
     </row>
+    <row r="3860">
+      <c r="A3860" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3860" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3860" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D3860" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3860" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3860"/>
+  <dimension ref="A1:E3861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104648,6 +104648,33 @@
         </is>
       </c>
     </row>
+    <row r="3861">
+      <c r="A3861" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3861" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3861" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3861" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3861" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3861"/>
+  <dimension ref="A1:E3862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104675,6 +104675,33 @@
         </is>
       </c>
     </row>
+    <row r="3862">
+      <c r="A3862" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3862" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3862" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3862" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3862" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3862"/>
+  <dimension ref="A1:E3863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104702,6 +104702,33 @@
         </is>
       </c>
     </row>
+    <row r="3863">
+      <c r="A3863" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3863" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3863" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3863" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3863" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3863"/>
+  <dimension ref="A1:E3864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104729,6 +104729,33 @@
         </is>
       </c>
     </row>
+    <row r="3864">
+      <c r="A3864" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3864" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3864" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3864" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3864" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3864"/>
+  <dimension ref="A1:E3865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104756,6 +104756,33 @@
         </is>
       </c>
     </row>
+    <row r="3865">
+      <c r="A3865" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3865" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3865" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3865" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3865" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3865"/>
+  <dimension ref="A1:E3866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104783,6 +104783,33 @@
         </is>
       </c>
     </row>
+    <row r="3866">
+      <c r="A3866" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3866" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3866" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3866" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3866" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3866"/>
+  <dimension ref="A1:E3867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104810,6 +104810,33 @@
         </is>
       </c>
     </row>
+    <row r="3867">
+      <c r="A3867" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3867" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3867" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3867" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3867" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3867"/>
+  <dimension ref="A1:E3868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104837,6 +104837,33 @@
         </is>
       </c>
     </row>
+    <row r="3868">
+      <c r="A3868" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3868" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3868" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3868" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3868" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3868"/>
+  <dimension ref="A1:E3869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104864,6 +104864,33 @@
         </is>
       </c>
     </row>
+    <row r="3869">
+      <c r="A3869" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3869" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3869" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3869" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3869" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3869"/>
+  <dimension ref="A1:E3870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104891,6 +104891,33 @@
         </is>
       </c>
     </row>
+    <row r="3870">
+      <c r="A3870" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3870" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3870" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3870" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E3870" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3870"/>
+  <dimension ref="A1:E3871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104918,6 +104918,33 @@
         </is>
       </c>
     </row>
+    <row r="3871">
+      <c r="A3871" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3871" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3871" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3871" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E3871" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3871"/>
+  <dimension ref="A1:E3872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104945,6 +104945,33 @@
         </is>
       </c>
     </row>
+    <row r="3872">
+      <c r="A3872" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3872" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3872" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3872" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3872" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3872"/>
+  <dimension ref="A1:E3873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104972,6 +104972,33 @@
         </is>
       </c>
     </row>
+    <row r="3873">
+      <c r="A3873" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3873" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3873" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D3873" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3873" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3873"/>
+  <dimension ref="A1:E3874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104999,6 +104999,33 @@
         </is>
       </c>
     </row>
+    <row r="3874">
+      <c r="A3874" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3874" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3874" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3874" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E3874" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3874"/>
+  <dimension ref="A1:E3875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105026,6 +105026,33 @@
         </is>
       </c>
     </row>
+    <row r="3875">
+      <c r="A3875" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3875" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3875" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3875" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3875" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3875"/>
+  <dimension ref="A1:E3876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105053,6 +105053,33 @@
         </is>
       </c>
     </row>
+    <row r="3876">
+      <c r="A3876" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B3876" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3876" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D3876" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3876" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3876"/>
+  <dimension ref="A1:E3877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105080,6 +105080,33 @@
         </is>
       </c>
     </row>
+    <row r="3877">
+      <c r="A3877" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B3877" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3877" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3877" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E3877" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3877"/>
+  <dimension ref="A1:E3878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105107,6 +105107,33 @@
         </is>
       </c>
     </row>
+    <row r="3878">
+      <c r="A3878" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B3878" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3878" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3878" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3878" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3878"/>
+  <dimension ref="A1:E3879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105134,6 +105134,33 @@
         </is>
       </c>
     </row>
+    <row r="3879">
+      <c r="A3879" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B3879" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3879" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3879" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3879" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3879"/>
+  <dimension ref="A1:E3880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105161,6 +105161,33 @@
         </is>
       </c>
     </row>
+    <row r="3880">
+      <c r="A3880" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B3880" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3880" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3880" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3880" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3880"/>
+  <dimension ref="A1:E3881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105188,6 +105188,33 @@
         </is>
       </c>
     </row>
+    <row r="3881">
+      <c r="A3881" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B3881" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3881" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3881" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3881" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3881"/>
+  <dimension ref="A1:E3882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105215,6 +105215,33 @@
         </is>
       </c>
     </row>
+    <row r="3882">
+      <c r="A3882" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3882" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3882" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D3882" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3882" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3882"/>
+  <dimension ref="A1:E3883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105242,6 +105242,33 @@
         </is>
       </c>
     </row>
+    <row r="3883">
+      <c r="A3883" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3883" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3883" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3883" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E3883" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3883"/>
+  <dimension ref="A1:E3884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105269,6 +105269,33 @@
         </is>
       </c>
     </row>
+    <row r="3884">
+      <c r="A3884" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3884" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3884" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3884" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E3884" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3884"/>
+  <dimension ref="A1:E3885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105296,6 +105296,33 @@
         </is>
       </c>
     </row>
+    <row r="3885">
+      <c r="A3885" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B3885" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3885" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D3885" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3885" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3885"/>
+  <dimension ref="A1:E3886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105323,6 +105323,33 @@
         </is>
       </c>
     </row>
+    <row r="3886">
+      <c r="A3886" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B3886" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3886" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3886" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3886" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3886"/>
+  <dimension ref="A1:E3887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105350,6 +105350,33 @@
         </is>
       </c>
     </row>
+    <row r="3887">
+      <c r="A3887" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B3887" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3887" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3887" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3887" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3887"/>
+  <dimension ref="A1:E3888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105377,6 +105377,33 @@
         </is>
       </c>
     </row>
+    <row r="3888">
+      <c r="A3888" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B3888" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3888" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3888" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3888" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3888"/>
+  <dimension ref="A1:E3889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105404,6 +105404,33 @@
         </is>
       </c>
     </row>
+    <row r="3889">
+      <c r="A3889" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B3889" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3889" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D3889" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3889" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3889"/>
+  <dimension ref="A1:E3890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105431,6 +105431,33 @@
         </is>
       </c>
     </row>
+    <row r="3890">
+      <c r="A3890" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B3890" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3890" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3890" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3890" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3890"/>
+  <dimension ref="A1:E3891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105458,6 +105458,33 @@
         </is>
       </c>
     </row>
+    <row r="3891">
+      <c r="A3891" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B3891" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3891" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D3891" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3891" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3891"/>
+  <dimension ref="A1:E3892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105485,6 +105485,33 @@
         </is>
       </c>
     </row>
+    <row r="3892">
+      <c r="A3892" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B3892" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3892" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3892" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3892" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3892"/>
+  <dimension ref="A1:E3893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105512,6 +105512,33 @@
         </is>
       </c>
     </row>
+    <row r="3893">
+      <c r="A3893" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B3893" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3893" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3893" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3893" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3893"/>
+  <dimension ref="A1:E3894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105539,6 +105539,33 @@
         </is>
       </c>
     </row>
+    <row r="3894">
+      <c r="A3894" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3894" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3894" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3894" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3894" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3894"/>
+  <dimension ref="A1:E3895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105566,6 +105566,33 @@
         </is>
       </c>
     </row>
+    <row r="3895">
+      <c r="A3895" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3895" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3895" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3895" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3895" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3895"/>
+  <dimension ref="A1:E3896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105593,6 +105593,33 @@
         </is>
       </c>
     </row>
+    <row r="3896">
+      <c r="A3896" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3896" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3896" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3896" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E3896" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3896"/>
+  <dimension ref="A1:E3897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105620,6 +105620,33 @@
         </is>
       </c>
     </row>
+    <row r="3897">
+      <c r="A3897" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3897" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3897" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D3897" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E3897" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3897"/>
+  <dimension ref="A1:E3898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105647,6 +105647,33 @@
         </is>
       </c>
     </row>
+    <row r="3898">
+      <c r="A3898" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3898" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3898" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3898" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3898" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3898"/>
+  <dimension ref="A1:E3899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105674,6 +105674,33 @@
         </is>
       </c>
     </row>
+    <row r="3899">
+      <c r="A3899" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3899" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3899" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3899" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E3899" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3899"/>
+  <dimension ref="A1:E3900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105701,6 +105701,33 @@
         </is>
       </c>
     </row>
+    <row r="3900">
+      <c r="A3900" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3900" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3900" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3900" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3900" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3900"/>
+  <dimension ref="A1:E3901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105728,6 +105728,33 @@
         </is>
       </c>
     </row>
+    <row r="3901">
+      <c r="A3901" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3901" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3901" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3901" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3901" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3901"/>
+  <dimension ref="A1:E3902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105755,6 +105755,33 @@
         </is>
       </c>
     </row>
+    <row r="3902">
+      <c r="A3902" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3902" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3902" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3902" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E3902" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3902"/>
+  <dimension ref="A1:E3903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105782,6 +105782,33 @@
         </is>
       </c>
     </row>
+    <row r="3903">
+      <c r="A3903" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B3903" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3903" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3903" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3903" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3903"/>
+  <dimension ref="A1:E3904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105809,6 +105809,33 @@
         </is>
       </c>
     </row>
+    <row r="3904">
+      <c r="A3904" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B3904" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3904" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3904" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E3904" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3904"/>
+  <dimension ref="A1:E3905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105836,6 +105836,33 @@
         </is>
       </c>
     </row>
+    <row r="3905">
+      <c r="A3905" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B3905" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3905" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D3905" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3905" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3905"/>
+  <dimension ref="A1:E3906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105863,6 +105863,33 @@
         </is>
       </c>
     </row>
+    <row r="3906">
+      <c r="A3906" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B3906" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3906" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D3906" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3906" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3906"/>
+  <dimension ref="A1:E3907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105890,6 +105890,33 @@
         </is>
       </c>
     </row>
+    <row r="3907">
+      <c r="A3907" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B3907" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3907" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3907" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3907" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3907"/>
+  <dimension ref="A1:E3908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105917,6 +105917,33 @@
         </is>
       </c>
     </row>
+    <row r="3908">
+      <c r="A3908" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B3908" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3908" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D3908" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3908" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3908"/>
+  <dimension ref="A1:E3909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105944,6 +105944,33 @@
         </is>
       </c>
     </row>
+    <row r="3909">
+      <c r="A3909" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B3909" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3909" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3909" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3909" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3909"/>
+  <dimension ref="A1:E3910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105971,6 +105971,33 @@
         </is>
       </c>
     </row>
+    <row r="3910">
+      <c r="A3910" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B3910" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3910" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3910" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3910" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3910"/>
+  <dimension ref="A1:E3911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105998,6 +105998,33 @@
         </is>
       </c>
     </row>
+    <row r="3911">
+      <c r="A3911" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B3911" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3911" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3911" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E3911" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3911"/>
+  <dimension ref="A1:E3912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106025,6 +106025,33 @@
         </is>
       </c>
     </row>
+    <row r="3912">
+      <c r="A3912" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3912" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3912" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3912" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3912" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3912"/>
+  <dimension ref="A1:E3913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106052,6 +106052,33 @@
         </is>
       </c>
     </row>
+    <row r="3913">
+      <c r="A3913" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3913" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3913" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3913" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E3913" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3913"/>
+  <dimension ref="A1:E3914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106079,6 +106079,33 @@
         </is>
       </c>
     </row>
+    <row r="3914">
+      <c r="A3914" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3914" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3914" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3914" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3914" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3914"/>
+  <dimension ref="A1:E3915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106106,6 +106106,33 @@
         </is>
       </c>
     </row>
+    <row r="3915">
+      <c r="A3915" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B3915" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3915" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3915" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3915" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3915"/>
+  <dimension ref="A1:E3916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106133,6 +106133,33 @@
         </is>
       </c>
     </row>
+    <row r="3916">
+      <c r="A3916" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B3916" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3916" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3916" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3916" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3916"/>
+  <dimension ref="A1:E3917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106160,6 +106160,33 @@
         </is>
       </c>
     </row>
+    <row r="3917">
+      <c r="A3917" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B3917" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3917" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3917" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3917" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3917"/>
+  <dimension ref="A1:E3918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106187,6 +106187,33 @@
         </is>
       </c>
     </row>
+    <row r="3918">
+      <c r="A3918" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3918" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3918" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3918" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E3918" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3918"/>
+  <dimension ref="A1:E3919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106214,6 +106214,33 @@
         </is>
       </c>
     </row>
+    <row r="3919">
+      <c r="A3919" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3919" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3919" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3919" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E3919" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3919"/>
+  <dimension ref="A1:E3920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106241,6 +106241,33 @@
         </is>
       </c>
     </row>
+    <row r="3920">
+      <c r="A3920" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3920" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3920" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3920" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3920" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3920"/>
+  <dimension ref="A1:E3921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106268,6 +106268,33 @@
         </is>
       </c>
     </row>
+    <row r="3921">
+      <c r="A3921" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B3921" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3921" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3921" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E3921" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3921"/>
+  <dimension ref="A1:E3922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106295,6 +106295,33 @@
         </is>
       </c>
     </row>
+    <row r="3922">
+      <c r="A3922" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B3922" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3922" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D3922" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3922" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3922"/>
+  <dimension ref="A1:E3923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106322,6 +106322,33 @@
         </is>
       </c>
     </row>
+    <row r="3923">
+      <c r="A3923" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B3923" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3923" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3923" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3923" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3923"/>
+  <dimension ref="A1:E3924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106349,6 +106349,33 @@
         </is>
       </c>
     </row>
+    <row r="3924">
+      <c r="A3924" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3924" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3924" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D3924" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3924" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3924"/>
+  <dimension ref="A1:E3929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106376,6 +106376,141 @@
         </is>
       </c>
     </row>
+    <row r="3925">
+      <c r="A3925" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3925" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3925" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3925" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3925" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="3926">
+      <c r="A3926" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3926" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3926" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3926" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3926" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="3927">
+      <c r="A3927" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B3927" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3927" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3927" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3927" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="3928">
+      <c r="A3928" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B3928" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3928" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3928" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3928" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3929">
+      <c r="A3929" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B3929" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3929" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3929" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3929" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
